--- a/tmp/roster_converted.xlsx
+++ b/tmp/roster_converted.xlsx
@@ -11703,10 +11703,10 @@
         <v>1</v>
       </c>
       <c r="F273">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G273" t="str">
-        <v>0745</v>
+        <v>745</v>
       </c>
       <c r="H273" t="str">
         <v>김동욱</v>
@@ -11744,10 +11744,10 @@
         <v>1</v>
       </c>
       <c r="F274">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G274" t="str">
-        <v>1762</v>
+        <v>762</v>
       </c>
       <c r="H274" t="str">
         <v>조민혁</v>
@@ -11785,10 +11785,10 @@
         <v>1</v>
       </c>
       <c r="F275">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G275" t="str">
-        <v>2516</v>
+        <v>516</v>
       </c>
       <c r="H275" t="str">
         <v>오준석</v>
@@ -11826,10 +11826,10 @@
         <v>1</v>
       </c>
       <c r="F276">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G276" t="str">
-        <v>3725</v>
+        <v>725</v>
       </c>
       <c r="H276" t="str">
         <v>이상윤</v>
@@ -11867,10 +11867,10 @@
         <v>1</v>
       </c>
       <c r="F277">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G277" t="str">
-        <v>4515</v>
+        <v>515</v>
       </c>
       <c r="H277" t="str">
         <v>오준서</v>
@@ -11908,10 +11908,10 @@
         <v>1</v>
       </c>
       <c r="F278">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G278" t="str">
-        <v>5813</v>
+        <v>813</v>
       </c>
       <c r="H278" t="str">
         <v>김지훈</v>
@@ -11949,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="F279">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G279" t="str">
-        <v>6501</v>
+        <v>501</v>
       </c>
       <c r="H279" t="str">
         <v>이영범</v>
@@ -11990,10 +11990,10 @@
         <v>1</v>
       </c>
       <c r="F280">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G280" t="str">
-        <v>7548</v>
+        <v>548</v>
       </c>
       <c r="H280" t="str">
         <v>정민국</v>
@@ -12400,10 +12400,10 @@
         <v>2</v>
       </c>
       <c r="F290">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G290" t="str">
-        <v>0569</v>
+        <v>569</v>
       </c>
       <c r="H290" t="str">
         <v>윤형준</v>
@@ -12441,10 +12441,10 @@
         <v>2</v>
       </c>
       <c r="F291">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G291" t="str">
-        <v>1570</v>
+        <v>570</v>
       </c>
       <c r="H291" t="str">
         <v>한예찬</v>
@@ -12482,10 +12482,10 @@
         <v>2</v>
       </c>
       <c r="F292">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G292" t="str">
-        <v>2686</v>
+        <v>686</v>
       </c>
       <c r="H292" t="str">
         <v>배상운</v>
@@ -12523,10 +12523,10 @@
         <v>2</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G293" t="str">
-        <v>3819</v>
+        <v>819</v>
       </c>
       <c r="H293" t="str">
         <v>윤준원</v>
@@ -12564,10 +12564,10 @@
         <v>2</v>
       </c>
       <c r="F294">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G294" t="str">
-        <v>4755</v>
+        <v>755</v>
       </c>
       <c r="H294" t="str">
         <v>이하늘</v>
@@ -12605,10 +12605,10 @@
         <v>2</v>
       </c>
       <c r="F295">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G295" t="str">
-        <v>5572</v>
+        <v>572</v>
       </c>
       <c r="H295" t="str">
         <v>장민</v>
@@ -12646,10 +12646,10 @@
         <v>2</v>
       </c>
       <c r="F296">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G296" t="str">
-        <v>6680</v>
+        <v>680</v>
       </c>
       <c r="H296" t="str">
         <v>김태영</v>
@@ -13056,10 +13056,10 @@
         <v/>
       </c>
       <c r="F306">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G306" t="str">
-        <v>0657</v>
+        <v>657</v>
       </c>
       <c r="H306" t="str">
         <v>우상혁</v>
@@ -13466,10 +13466,10 @@
         <v/>
       </c>
       <c r="F316">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G316" t="str">
-        <v>0732</v>
+        <v>732</v>
       </c>
       <c r="H316" t="str">
         <v>이현우</v>
@@ -13507,10 +13507,10 @@
         <v/>
       </c>
       <c r="F317">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G317" t="str">
-        <v>1779</v>
+        <v>779</v>
       </c>
       <c r="H317" t="str">
         <v>조홍조</v>
@@ -13548,10 +13548,10 @@
         <v/>
       </c>
       <c r="F318">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G318" t="str">
-        <v>2753</v>
+        <v>753</v>
       </c>
       <c r="H318" t="str">
         <v>심지민</v>
@@ -13589,10 +13589,10 @@
         <v/>
       </c>
       <c r="F319">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G319" t="str">
-        <v>3601</v>
+        <v>601</v>
       </c>
       <c r="H319" t="str">
         <v>성진석</v>
@@ -24003,10 +24003,10 @@
         <v/>
       </c>
       <c r="F573">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G573" t="str">
-        <v>0307</v>
+        <v>307</v>
       </c>
       <c r="H573" t="str">
         <v>유형원</v>
@@ -24044,10 +24044,10 @@
         <v/>
       </c>
       <c r="F574">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G574" t="str">
-        <v>1348</v>
+        <v>348</v>
       </c>
       <c r="H574" t="str">
         <v>김강민</v>
@@ -24085,10 +24085,10 @@
         <v/>
       </c>
       <c r="F575">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G575" t="str">
-        <v>2381</v>
+        <v>381</v>
       </c>
       <c r="H575" t="str">
         <v>신재호</v>
@@ -24126,10 +24126,10 @@
         <v/>
       </c>
       <c r="F576">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G576" t="str">
-        <v>3355</v>
+        <v>355</v>
       </c>
       <c r="H576" t="str">
         <v>김상형</v>
